--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T75731054-000003</x:t>
+    <x:t>T096B5447-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T75731054-000005</x:t>
+    <x:t>T096B5447-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T096B5447-000003</x:t>
+    <x:t>T045134E4-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T096B5447-000005</x:t>
+    <x:t>T045134E4-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T045134E4-000003</x:t>
+    <x:t>T6E90C249-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T045134E4-000005</x:t>
+    <x:t>T6E90C249-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T6E90C249-000003</x:t>
+    <x:t>T1D0893C6-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T6E90C249-000005</x:t>
+    <x:t>T1D0893C6-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T1D0893C6-000003</x:t>
+    <x:t>T7C19E4E8-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T1D0893C6-000005</x:t>
+    <x:t>T7C19E4E8-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T7C19E4E8-000003</x:t>
+    <x:t>T3DC6A6CA-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T7C19E4E8-000005</x:t>
+    <x:t>T3DC6A6CA-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T3DC6A6CA-000003</x:t>
+    <x:t>TD13AB0E1-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T3DC6A6CA-000005</x:t>
+    <x:t>TD13AB0E1-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TD13AB0E1-000003</x:t>
+    <x:t>TF9CA655A-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>TD13AB0E1-000005</x:t>
+    <x:t>TF9CA655A-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TF9CA655A-000003</x:t>
+    <x:t>T720C2400-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>TF9CA655A-000005</x:t>
+    <x:t>T720C2400-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T720C2400-000003</x:t>
+    <x:t>T351587C5-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T720C2400-000005</x:t>
+    <x:t>T351587C5-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-approved-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T351587C5-000003</x:t>
+    <x:t>TE894F53D-000003</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -51,7 +51,7 @@
     <x:t>private 2</x:t>
   </x:si>
   <x:si>
-    <x:t>T351587C5-000005</x:t>
+    <x:t>TE894F53D-000005</x:t>
   </x:si>
   <x:si>
     <x:t>private 4</x:t>
